--- a/tests/unit/apps/registration_data/test_file/rdi_people_test.xlsx
+++ b/tests/unit/apps/registration_data/test_file/rdi_people_test.xlsx
@@ -1144,13 +1144,13 @@
     <t>facility_admin_area_h_c</t>
   </si>
   <si>
-    <t>Collector ForJanIndex_3</t>
+    <t>Collector ForJanIndexThree</t>
   </si>
   <si>
     <t>Collector</t>
   </si>
   <si>
-    <t>ForJanIndex_3</t>
+    <t>ForJanIndexThree</t>
   </si>
   <si>
     <t>MALE</t>
@@ -1255,13 +1255,13 @@
     <t>2.99</t>
   </si>
   <si>
-    <t>WorkerCollector ForDerekIndex_4</t>
+    <t>WorkerCollector ForDerekIndexFour</t>
   </si>
   <si>
     <t>WorkerCollector</t>
   </si>
   <si>
-    <t>ForDerekIndex_4</t>
+    <t>ForDerekIndexFour</t>
   </si>
   <si>
     <t>3</t>
@@ -1273,13 +1273,13 @@
     <t>Name1</t>
   </si>
   <si>
-    <t>Jan    Index3</t>
+    <t>Jan IndexThree</t>
   </si>
   <si>
     <t>Jan</t>
   </si>
   <si>
-    <t>Index3</t>
+    <t>IndexThree</t>
   </si>
   <si>
     <t>FEMALE</t>
@@ -1300,25 +1300,25 @@
     <t>New School 23</t>
   </si>
   <si>
-    <t>Derek Index4</t>
+    <t>Derek IndexFour</t>
   </si>
   <si>
     <t>Derek</t>
   </si>
   <si>
-    <t>Index4</t>
+    <t>IndexFour</t>
   </si>
   <si>
     <t>Test PDU Value</t>
   </si>
   <si>
-    <t>Test Index5</t>
+    <t>Test IndexFive</t>
   </si>
   <si>
     <t>Test</t>
   </si>
   <si>
-    <t>Index5</t>
+    <t>IndexFive</t>
   </si>
   <si>
     <t>5</t>

--- a/tests/unit/apps/registration_data/test_file/rdi_people_test.xlsx
+++ b/tests/unit/apps/registration_data/test_file/rdi_people_test.xlsx
@@ -1144,13 +1144,13 @@
     <t>facility_admin_area_h_c</t>
   </si>
   <si>
-    <t>Collector ForJanIndexThree</t>
+    <t>Collector ForJanIndex_3</t>
   </si>
   <si>
     <t>Collector</t>
   </si>
   <si>
-    <t>ForJanIndexThree</t>
+    <t>ForJanIndex_3</t>
   </si>
   <si>
     <t>MALE</t>
@@ -1255,13 +1255,13 @@
     <t>2.99</t>
   </si>
   <si>
-    <t>WorkerCollector ForDerekIndexFour</t>
+    <t>WorkerCollector ForDerekIndex_4</t>
   </si>
   <si>
     <t>WorkerCollector</t>
   </si>
   <si>
-    <t>ForDerekIndexFour</t>
+    <t>ForDerekIndex_4</t>
   </si>
   <si>
     <t>3</t>
@@ -1273,13 +1273,13 @@
     <t>Name1</t>
   </si>
   <si>
-    <t>Jan IndexThree</t>
+    <t>Jan    Index3</t>
   </si>
   <si>
     <t>Jan</t>
   </si>
   <si>
-    <t>IndexThree</t>
+    <t>Index3</t>
   </si>
   <si>
     <t>FEMALE</t>
@@ -1300,25 +1300,25 @@
     <t>New School 23</t>
   </si>
   <si>
-    <t>Derek IndexFour</t>
+    <t>Derek Index4</t>
   </si>
   <si>
     <t>Derek</t>
   </si>
   <si>
-    <t>IndexFour</t>
+    <t>Index4</t>
   </si>
   <si>
     <t>Test PDU Value</t>
   </si>
   <si>
-    <t>Test IndexFive</t>
+    <t>Test Index5</t>
   </si>
   <si>
     <t>Test</t>
   </si>
   <si>
-    <t>IndexFive</t>
+    <t>Index5</t>
   </si>
   <si>
     <t>5</t>
